--- a/action_cop/output_excels/21_Related_Party_Transactions.xlsx
+++ b/action_cop/output_excels/21_Related_Party_Transactions.xlsx
@@ -845,7 +845,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -954,12 +954,12 @@
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t>18-JUN-2026 14:18:20</t>
+          <t>18-JUN-2026 14:18:22</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>00:00:03</t>
+          <t>00:00:05</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1093,12 +1093,12 @@
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
-          <t>17-JUN-2026 19:26:39</t>
+          <t>17-JUN-2026 19:26:40</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>00:00:03</t>
+          <t>00:00:04</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1649,12 +1649,12 @@
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>13-MAR-2026 08:57:24</t>
+          <t>13-MAR-2026 08:57:25</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>00:00:03</t>
+          <t>00:00:04</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1788,12 +1788,12 @@
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>13-MAR-2026 08:56:26</t>
+          <t>13-MAR-2026 08:56:27</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>00:00:03</t>
+          <t>00:00:04</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2066,12 +2066,12 @@
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
         <is>
-          <t>12-MAR-2026 17:23:12</t>
+          <t>12-MAR-2026 17:23:13</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>00:00:03</t>
+          <t>00:00:04</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2205,12 +2205,12 @@
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr">
         <is>
-          <t>19-FEB-2026 18:06:05</t>
+          <t>19-FEB-2026 18:06:06</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>00:00:03</t>
+          <t>00:00:04</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2378,7 +2378,7 @@
       <c r="AA14" t="inlineStr"/>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2521,7 +2521,7 @@
       <c r="AA15" t="inlineStr"/>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2656,7 +2656,7 @@
       <c r="AA16" t="inlineStr"/>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2765,12 +2765,12 @@
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr">
         <is>
-          <t>20-MAY-2025 22:48:14</t>
+          <t>20-MAY-2025 22:48:13</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>00:00:04</t>
+          <t>00:00:03</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -2791,7 +2791,7 @@
       <c r="AA17" t="inlineStr"/>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2900,12 +2900,12 @@
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr">
         <is>
-          <t>20-MAY-2025 15:57:17</t>
+          <t>20-MAY-2025 15:57:18</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>00:00:03</t>
+          <t>00:00:04</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -2926,7 +2926,7 @@
       <c r="AA18" t="inlineStr"/>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -3035,12 +3035,12 @@
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr">
         <is>
-          <t>20-MAY-2025 15:26:01</t>
+          <t>20-MAY-2025 15:26:02</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>00:00:03</t>
+          <t>00:00:04</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -3061,7 +3061,7 @@
       <c r="AA19" t="inlineStr"/>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3170,12 +3170,12 @@
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr">
         <is>
-          <t>09-MAY-2025 22:12:11</t>
+          <t>09-MAY-2025 22:12:12</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>00:00:02</t>
+          <t>00:00:03</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -3196,7 +3196,7 @@
       <c r="AA20" t="inlineStr"/>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3339,7 +3339,7 @@
       <c r="AA21" t="inlineStr"/>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3448,12 +3448,12 @@
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr">
         <is>
-          <t>09-MAY-2025 16:59:48</t>
+          <t>09-MAY-2025 16:59:49</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>00:00:03</t>
+          <t>00:00:04</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -3474,7 +3474,7 @@
       <c r="AA22" t="inlineStr"/>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
